--- a/public/templates/forms/HRMS-PD Form 02.xlsx
+++ b/public/templates/forms/HRMS-PD Form 02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carl Llemos\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C5A3AB9-B602-46D5-A0A7-8F59E09A2390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0AF664E-FF49-4E16-9A2B-1CB71DCBAB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -89,7 +89,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -137,13 +137,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -282,12 +275,38 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -297,77 +316,110 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -683,576 +735,631 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="28"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="5"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="6" t="s">
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="6" t="s">
+      <c r="E4" s="9"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="7"/>
-      <c r="I4" s="8"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="10"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="23"/>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="20"/>
+      <c r="A5" s="35"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="39"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7" t="s">
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="2" t="s">
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="8"/>
+      <c r="I6" s="10"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="12"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="11"/>
+      <c r="A7" s="37"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="44"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="6" t="s">
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="8"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="10"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="16"/>
+      <c r="A9" s="23"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="31"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="12"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="19"/>
+      <c r="A10" s="26"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="34"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="6" t="s">
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="8"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="10"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="6" t="s">
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="8"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="10"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="11"/>
+      <c r="A13" s="14"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="16"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="11"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="16"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="3" t="s">
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="5"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="13"/>
     </row>
     <row r="17" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="29"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="28"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="5"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="6" t="s">
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="7"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="6" t="s">
+      <c r="E19" s="9"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="7"/>
-      <c r="I19" s="8"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="10"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="23"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="20"/>
+      <c r="A20" s="45"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="22"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7" t="s">
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="2" t="s">
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I21" s="8"/>
+      <c r="I21" s="10"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="12"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="11"/>
+      <c r="A22" s="20"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="19"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="6" t="s">
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="8"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="10"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="9"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="16"/>
+      <c r="A24" s="23"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="31"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="12"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="19"/>
+      <c r="A25" s="26"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="34"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="6" t="s">
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="8"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="10"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="6" t="s">
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="8"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="10"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="9"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="11"/>
+      <c r="A28" s="14"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="16"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="9"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="11"/>
+      <c r="A29" s="14"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="16"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="3" t="s">
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="5"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="13"/>
     </row>
     <row r="32" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="29" t="s">
+      <c r="A32" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="26" t="s">
+      <c r="A33" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B33" s="27"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="28"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="5"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="21" t="s">
+      <c r="A34" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="22"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="6" t="s">
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E34" s="7"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="6" t="s">
+      <c r="E34" s="9"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H34" s="7"/>
-      <c r="I34" s="8"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="10"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="23"/>
-      <c r="B35" s="24"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="20"/>
+      <c r="A35" s="45"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="46"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="22"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7" t="s">
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="2" t="s">
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H36" s="6" t="s">
+      <c r="H36" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I36" s="8"/>
+      <c r="I36" s="10"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="12"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="11"/>
+      <c r="A37" s="20"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="19"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="6" t="s">
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="8"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="10"/>
     </row>
     <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="9"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="16"/>
+      <c r="A39" s="23"/>
+      <c r="B39" s="24"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="31"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="12"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="19"/>
+      <c r="A40" s="26"/>
+      <c r="B40" s="27"/>
+      <c r="C40" s="27"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="33"/>
+      <c r="H40" s="33"/>
+      <c r="I40" s="34"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="6" t="s">
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
-      <c r="I41" s="8"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="10"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="6" t="s">
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="8"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="10"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="9"/>
-      <c r="B43" s="10"/>
-      <c r="C43" s="10"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="11"/>
+      <c r="A43" s="14"/>
+      <c r="B43" s="15"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="15"/>
+      <c r="I43" s="16"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="9"/>
-      <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="11"/>
+      <c r="A44" s="14"/>
+      <c r="B44" s="15"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="15"/>
+      <c r="H44" s="15"/>
+      <c r="I44" s="16"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="3" t="s">
+      <c r="B45" s="12"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="5"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
+      <c r="I45" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="F45:I45"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="F42:I42"/>
+    <mergeCell ref="A43:E44"/>
+    <mergeCell ref="F43:I44"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="F41:I41"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="F39:I40"/>
+    <mergeCell ref="A39:E40"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="F30:I30"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A28:E29"/>
+    <mergeCell ref="F28:I29"/>
+    <mergeCell ref="F24:I25"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="A24:E25"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="A13:E14"/>
+    <mergeCell ref="F13:I14"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="F11:I11"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="F8:I8"/>
     <mergeCell ref="F9:I10"/>
@@ -1266,66 +1373,11 @@
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="H7:I7"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="F12:I12"/>
-    <mergeCell ref="A13:E14"/>
-    <mergeCell ref="F13:I14"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="F24:I25"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="A24:E25"/>
-    <mergeCell ref="A33:I33"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="F30:I30"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A28:E29"/>
-    <mergeCell ref="F28:I29"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="F41:I41"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="F38:I38"/>
-    <mergeCell ref="F39:I40"/>
-    <mergeCell ref="A39:E40"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="F45:I45"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="F42:I42"/>
-    <mergeCell ref="A43:E44"/>
-    <mergeCell ref="F43:I44"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:I4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="120" verticalDpi="72" r:id="rId1"/>
